--- a/reports/SF_FC_Furniture_Details_2026.xlsx
+++ b/reports/SF_FC_Furniture_Details_2026.xlsx
@@ -13,7 +13,18 @@
     <sheet name="SFFC Leather Sofa" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="SF FC Summery" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'SF FC External'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'SF FC External'!$A$1:$I$14</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'SFFC Chairs In Use'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'SFFC Chairs In Use'!$A$1:$L$18</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'SFFC Tables In Use'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'SFFC Tables In Use'!$A$1:$H$18</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'SFFC Leather Sofa'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'SFFC Leather Sofa'!$A$1:$F$7</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'SF FC Summery'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'SF FC Summery'!$A$1:$H$5</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -71,7 +82,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -133,11 +144,17 @@
       <bottom style="thin"/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -146,8 +163,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -523,7 +544,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -735,80 +756,89 @@
       </c>
       <c r="I8" s="2" t="n"/>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Source header block (rows 1-5, superseded)</t>
         </is>
       </c>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n"/>
+      <c r="I10" s="5" t="n"/>
     </row>
     <row r="11" ht="25" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">SF Food Court External Chairs </t>
         </is>
       </c>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n"/>
+      <c r="B11" s="7" t="n"/>
+      <c r="C11" s="7" t="n"/>
+      <c r="D11" s="7" t="n"/>
+      <c r="E11" s="7" t="n"/>
     </row>
     <row r="12" ht="25" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">KFC Terrace  </t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Dome Seating  Area </t>
         </is>
       </c>
-      <c r="C12" s="5" t="n">
+      <c r="C12" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">burger king Terrace </t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>Total On the floor</t>
         </is>
       </c>
     </row>
     <row r="13" ht="25" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">SF Food Court External Table </t>
         </is>
       </c>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
+      <c r="B13" s="7" t="n"/>
+      <c r="C13" s="7" t="n"/>
+      <c r="D13" s="7" t="n"/>
+      <c r="E13" s="7" t="n"/>
     </row>
     <row r="14" ht="25" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">KFC Terrace  </t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Dome Seating  Area </t>
         </is>
       </c>
-      <c r="C14" s="5" t="n">
+      <c r="C14" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">burger king Terrace </t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
         <is>
           <t>Total On the floor</t>
         </is>
@@ -831,6 +861,7 @@
     <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -838,7 +869,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1138,120 +1169,120 @@
       <c r="L15" s="2" t="n"/>
     </row>
     <row r="16" ht="25" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Total on the floor  </t>
         </is>
       </c>
-      <c r="B16" s="7">
+      <c r="B16" s="9">
         <f>SUM(B3:B15)</f>
         <v/>
       </c>
-      <c r="C16" s="7">
+      <c r="C16" s="9">
         <f>SUM(C3:C15)</f>
         <v/>
       </c>
-      <c r="D16" s="7">
+      <c r="D16" s="9">
         <f>SUM(D3:D15)</f>
         <v/>
       </c>
-      <c r="E16" s="7">
+      <c r="E16" s="9">
         <f>SUM(E3:E15)</f>
         <v/>
       </c>
-      <c r="F16" s="7">
+      <c r="F16" s="9">
         <f>SUM(F3:F15)</f>
         <v/>
       </c>
-      <c r="G16" s="7">
+      <c r="G16" s="9">
         <f>SUM(G3:G15)</f>
         <v/>
       </c>
-      <c r="H16" s="7">
+      <c r="H16" s="9">
         <f>SUM(H3:H15)</f>
         <v/>
       </c>
-      <c r="I16" s="7">
+      <c r="I16" s="9">
         <f>SUM(I3:I15)</f>
         <v/>
       </c>
-      <c r="J16" s="7" t="n">
+      <c r="J16" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="K16" s="7">
+      <c r="K16" s="9">
         <f>SUM(B16:J16)</f>
         <v/>
       </c>
-      <c r="L16" s="7" t="n"/>
+      <c r="L16" s="9" t="n"/>
     </row>
     <row r="17" ht="25" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Stock in store </t>
         </is>
       </c>
-      <c r="B17" s="7" t="n"/>
-      <c r="C17" s="7" t="n"/>
-      <c r="D17" s="7" t="n"/>
-      <c r="E17" s="7" t="n"/>
-      <c r="F17" s="7" t="n"/>
-      <c r="G17" s="7" t="n"/>
-      <c r="H17" s="7" t="n"/>
-      <c r="I17" s="7" t="n"/>
-      <c r="J17" s="7" t="n"/>
-      <c r="K17" s="7">
+      <c r="B17" s="9" t="n"/>
+      <c r="C17" s="9" t="n"/>
+      <c r="D17" s="9" t="n"/>
+      <c r="E17" s="9" t="n"/>
+      <c r="F17" s="9" t="n"/>
+      <c r="G17" s="9" t="n"/>
+      <c r="H17" s="9" t="n"/>
+      <c r="I17" s="9" t="n"/>
+      <c r="J17" s="9" t="n"/>
+      <c r="K17" s="9">
         <f>SUM(B17:I17)</f>
         <v/>
       </c>
-      <c r="L17" s="7" t="n"/>
+      <c r="L17" s="9" t="n"/>
     </row>
     <row r="18" ht="25" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Available stock </t>
         </is>
       </c>
-      <c r="B18" s="7">
+      <c r="B18" s="9">
         <f>SUM(B16+B17)</f>
         <v/>
       </c>
-      <c r="C18" s="7">
+      <c r="C18" s="9">
         <f>SUM(C16+C17)</f>
         <v/>
       </c>
-      <c r="D18" s="7">
+      <c r="D18" s="9">
         <f>SUM(D16+D17)</f>
         <v/>
       </c>
-      <c r="E18" s="7">
+      <c r="E18" s="9">
         <f>SUM(E16+E17)</f>
         <v/>
       </c>
-      <c r="F18" s="7">
+      <c r="F18" s="9">
         <f>SUM(F16+F17)</f>
         <v/>
       </c>
-      <c r="G18" s="7">
+      <c r="G18" s="9">
         <f>SUM(G16+G17)</f>
         <v/>
       </c>
-      <c r="H18" s="7">
+      <c r="H18" s="9">
         <f>SUM(H16+H17)</f>
         <v/>
       </c>
-      <c r="I18" s="7">
+      <c r="I18" s="9">
         <f>SUM(I16+I17)</f>
         <v/>
       </c>
-      <c r="J18" s="7">
+      <c r="J18" s="9">
         <f>SUM(J16+J17)</f>
         <v/>
       </c>
-      <c r="K18" s="7">
+      <c r="K18" s="9">
         <f>SUM(K16+K17)</f>
         <v/>
       </c>
-      <c r="L18" s="7" t="n"/>
+      <c r="L18" s="9" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -1269,6 +1300,7 @@
     <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1276,7 +1308,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1488,89 +1520,89 @@
       <c r="H15" s="2" t="n"/>
     </row>
     <row r="16" ht="25" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Total On The floor </t>
         </is>
       </c>
-      <c r="B16" s="7">
+      <c r="B16" s="9">
         <f>SUM(B3:B15)</f>
         <v/>
       </c>
-      <c r="C16" s="7">
+      <c r="C16" s="9">
         <f>SUM(C3:C15)</f>
         <v/>
       </c>
-      <c r="D16" s="7">
+      <c r="D16" s="9">
         <f>SUM(D3:D15)</f>
         <v/>
       </c>
-      <c r="E16" s="7">
+      <c r="E16" s="9">
         <f>SUM(E3:E15)</f>
         <v/>
       </c>
-      <c r="F16" s="7">
+      <c r="F16" s="9">
         <f>SUM(F3:F15)</f>
         <v/>
       </c>
-      <c r="G16" s="7">
+      <c r="G16" s="9">
         <f>SUM(B16:F16)</f>
         <v/>
       </c>
-      <c r="H16" s="7" t="n"/>
+      <c r="H16" s="9" t="n"/>
     </row>
     <row r="17" ht="25" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Stock in store </t>
         </is>
       </c>
-      <c r="B17" s="7" t="n"/>
-      <c r="C17" s="7" t="n"/>
-      <c r="D17" s="7" t="n"/>
-      <c r="E17" s="7" t="n"/>
-      <c r="F17" s="7" t="n"/>
-      <c r="G17" s="7">
+      <c r="B17" s="9" t="n"/>
+      <c r="C17" s="9" t="n"/>
+      <c r="D17" s="9" t="n"/>
+      <c r="E17" s="9" t="n"/>
+      <c r="F17" s="9" t="n"/>
+      <c r="G17" s="9">
         <f>SUM(B17:F17)</f>
         <v/>
       </c>
-      <c r="H17" s="7" t="inlineStr">
+      <c r="H17" s="9" t="inlineStr">
         <is>
           <t>Source formula was =SUM(I18:P18), which spans columns outside the tables block; both evaluate to 0</t>
         </is>
       </c>
     </row>
     <row r="18" ht="25" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Available stock </t>
         </is>
       </c>
-      <c r="B18" s="7">
+      <c r="B18" s="9">
         <f>SUM(B16+B17)</f>
         <v/>
       </c>
-      <c r="C18" s="7">
+      <c r="C18" s="9">
         <f>SUM(C16+C17)</f>
         <v/>
       </c>
-      <c r="D18" s="7">
+      <c r="D18" s="9">
         <f>SUM(D16+D17)</f>
         <v/>
       </c>
-      <c r="E18" s="7">
+      <c r="E18" s="9">
         <f>SUM(E16+E17)</f>
         <v/>
       </c>
-      <c r="F18" s="7">
+      <c r="F18" s="9">
         <f>SUM(F16+F17)</f>
         <v/>
       </c>
-      <c r="G18" s="7">
+      <c r="G18" s="9">
         <f>SUM(B18:F18)</f>
         <v/>
       </c>
-      <c r="H18" s="7" t="n"/>
+      <c r="H18" s="9" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -1584,6 +1616,7 @@
     <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1591,7 +1624,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1741,15 +1774,15 @@
       <c r="F6" s="2" t="n"/>
     </row>
     <row r="7" ht="25" customHeight="1">
-      <c r="A7" s="6" t="n"/>
-      <c r="B7" s="8" t="n"/>
-      <c r="C7" s="7" t="n"/>
-      <c r="D7" s="7" t="n"/>
-      <c r="E7" s="7">
+      <c r="A7" s="8" t="n"/>
+      <c r="B7" s="10" t="n"/>
+      <c r="C7" s="9" t="n"/>
+      <c r="D7" s="9" t="n"/>
+      <c r="E7" s="9">
         <f>SUM(E3:E6)</f>
         <v/>
       </c>
-      <c r="F7" s="7" t="n"/>
+      <c r="F7" s="9" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -1762,6 +1795,7 @@
     <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1769,7 +1803,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1878,9 +1912,9 @@
         <v>719</v>
       </c>
       <c r="D4" s="3" t="n"/>
-      <c r="E4" s="9" t="n"/>
-      <c r="F4" s="9" t="n"/>
-      <c r="G4" s="9" t="n"/>
+      <c r="E4" s="11" t="n"/>
+      <c r="F4" s="11" t="n"/>
+      <c r="G4" s="11" t="n"/>
       <c r="H4" s="2" t="n"/>
     </row>
     <row r="5" ht="25" customHeight="1">
@@ -1917,5 +1951,6 @@
     <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>